--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-practitioner.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-practitioner.xlsx
@@ -1220,7 +1220,7 @@
 医籍登録番号のsystemはFixed Valueの http://jpfhir.jp/fhir/core/mhlw/IdSystem/medicalRegistrationNumber を使用する。</t>
   </si>
   <si>
-    <t xml:space="preserve">value:code}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
